--- a/data/industry/CFM/UFS.xlsx
+++ b/data/industry/CFM/UFS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E7DCA8-45E0-4170-8C9C-E866B5DE2E07}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA43A636-68F9-41F4-8FE0-2D68AC17568B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -453,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1094,7 +1094,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -1107,6 +1107,121 @@
       </c>
       <c r="G28" s="10">
         <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>19.3</v>
+      </c>
+      <c r="F29" s="10">
+        <v>21</v>
+      </c>
+      <c r="G29" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>19.3</v>
+      </c>
+      <c r="F30" s="10">
+        <v>21</v>
+      </c>
+      <c r="G30" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>19.3</v>
+      </c>
+      <c r="F31" s="10">
+        <v>21</v>
+      </c>
+      <c r="G31" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="F32" s="10">
+        <v>26</v>
+      </c>
+      <c r="G32" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F33" s="10">
+        <v>28</v>
+      </c>
+      <c r="G33" s="10">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9244C5-F48F-43B7-9154-783F9DA9F8C6}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1758,7 +1873,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -1771,6 +1886,121 @@
       </c>
       <c r="G28" s="12">
         <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>29.8</v>
+      </c>
+      <c r="F29" s="12">
+        <v>32.5</v>
+      </c>
+      <c r="G29" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>29.8</v>
+      </c>
+      <c r="F30" s="12">
+        <v>32.5</v>
+      </c>
+      <c r="G30" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>29.8</v>
+      </c>
+      <c r="F31" s="12">
+        <v>32.5</v>
+      </c>
+      <c r="G31" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F32" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G32" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F33" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G33" s="12">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6478684B-CAE8-48EE-80F6-6A07A9D856F1}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2422,7 +2652,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -2435,6 +2665,121 @@
       </c>
       <c r="G28" s="10">
         <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>50.7</v>
+      </c>
+      <c r="F29" s="10">
+        <v>55</v>
+      </c>
+      <c r="G29" s="10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>50.7</v>
+      </c>
+      <c r="F30" s="10">
+        <v>55</v>
+      </c>
+      <c r="G30" s="10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>50.7</v>
+      </c>
+      <c r="F31" s="10">
+        <v>55</v>
+      </c>
+      <c r="G31" s="10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F32" s="10">
+        <v>63</v>
+      </c>
+      <c r="G32" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F33" s="10">
+        <v>63</v>
+      </c>
+      <c r="G33" s="10">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9291558D-A342-4E30-81D9-3EB746F72AE7}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -3086,7 +3431,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="6">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
@@ -3099,6 +3444,121 @@
       </c>
       <c r="G28" s="10">
         <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="F29" s="10">
+        <v>75</v>
+      </c>
+      <c r="G29" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="F30" s="10">
+        <v>75</v>
+      </c>
+      <c r="G30" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="F31" s="10">
+        <v>75</v>
+      </c>
+      <c r="G31" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F32" s="10">
+        <v>93</v>
+      </c>
+      <c r="G32" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F33" s="10">
+        <v>93</v>
+      </c>
+      <c r="G33" s="10">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/UFS.xlsx
+++ b/data/industry/CFM/UFS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2812DA68-12BE-4A02-9A19-87A5E5318354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BA7725-8FD0-43CF-9EE4-EFD522245A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -70,25 +70,25 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -101,7 +101,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -132,45 +132,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -453,19 +453,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -511,7 +511,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -534,7 +534,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -557,7 +557,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -580,7 +580,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -603,7 +603,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -626,7 +626,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -649,7 +649,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -672,7 +672,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -695,7 +695,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -718,7 +718,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -741,7 +741,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -764,7 +764,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -787,7 +787,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -810,7 +810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -833,7 +833,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -856,7 +856,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -879,7 +879,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -902,7 +902,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -925,7 +925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -971,7 +971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -994,7 +994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -1359,6 +1359,144 @@
         <v>28</v>
       </c>
       <c r="G39" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F40" s="10">
+        <v>28</v>
+      </c>
+      <c r="G40" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F41" s="10">
+        <v>28</v>
+      </c>
+      <c r="G41" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F42" s="10">
+        <v>28</v>
+      </c>
+      <c r="G42" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F43" s="10">
+        <v>28</v>
+      </c>
+      <c r="G43" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F44" s="10">
+        <v>28</v>
+      </c>
+      <c r="G44" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>26.3</v>
+      </c>
+      <c r="F45" s="10">
+        <v>28</v>
+      </c>
+      <c r="G45" s="10">
         <v>27</v>
       </c>
     </row>
@@ -1370,19 +1508,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE9244C5-F48F-43B7-9154-783F9DA9F8C6}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1405,7 +1543,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -1428,7 +1566,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -1451,7 +1589,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1474,7 +1612,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -1497,7 +1635,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -1520,7 +1658,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -1543,7 +1681,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -1566,7 +1704,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -1589,7 +1727,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -1612,7 +1750,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -1635,7 +1773,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -1658,7 +1796,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -1681,7 +1819,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -1704,7 +1842,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -1727,7 +1865,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -1750,7 +1888,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -1773,7 +1911,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -1796,7 +1934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -1819,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -1842,7 +1980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -1865,7 +2003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -1888,7 +2026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -1911,7 +2049,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1934,7 +2072,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1957,7 +2095,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1980,7 +2118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2003,7 +2141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -2026,7 +2164,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2049,7 +2187,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2072,7 +2210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -2095,7 +2233,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -2118,7 +2256,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -2141,7 +2279,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -2164,7 +2302,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -2187,7 +2325,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -2210,7 +2348,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -2233,7 +2371,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -2256,7 +2394,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -2276,6 +2414,144 @@
         <v>35.5</v>
       </c>
       <c r="G39" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F40" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G40" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F41" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G41" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F42" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G42" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F43" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G43" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F44" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G44" s="12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F45" s="12">
+        <v>35.5</v>
+      </c>
+      <c r="G45" s="12">
         <v>33</v>
       </c>
     </row>
@@ -2287,19 +2563,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6478684B-CAE8-48EE-80F6-6A07A9D856F1}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2598,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -2345,7 +2621,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -2368,7 +2644,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2391,7 +2667,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -2414,7 +2690,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -2437,7 +2713,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -2460,7 +2736,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -2483,7 +2759,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -2506,7 +2782,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -2529,7 +2805,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -2552,7 +2828,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -2575,7 +2851,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -2598,7 +2874,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -2621,7 +2897,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -2644,7 +2920,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -2667,7 +2943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -2690,7 +2966,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -2713,7 +2989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -2736,7 +3012,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -2759,7 +3035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -2782,7 +3058,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -2805,7 +3081,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -2828,7 +3104,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -2851,7 +3127,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -2874,7 +3150,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -2897,7 +3173,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2920,7 +3196,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -2943,7 +3219,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2966,7 +3242,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2989,7 +3265,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3012,7 +3288,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3035,7 +3311,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3058,7 +3334,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3081,7 +3357,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -3104,7 +3380,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -3127,7 +3403,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -3150,7 +3426,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -3173,7 +3449,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -3193,6 +3469,144 @@
         <v>63</v>
       </c>
       <c r="G39" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F40" s="10">
+        <v>63</v>
+      </c>
+      <c r="G40" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F41" s="10">
+        <v>63</v>
+      </c>
+      <c r="G41" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F42" s="10">
+        <v>63</v>
+      </c>
+      <c r="G42" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F43" s="10">
+        <v>63</v>
+      </c>
+      <c r="G43" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F44" s="10">
+        <v>63</v>
+      </c>
+      <c r="G44" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>58.7</v>
+      </c>
+      <c r="F45" s="10">
+        <v>63</v>
+      </c>
+      <c r="G45" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3204,19 +3618,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9291558D-A342-4E30-81D9-3EB746F72AE7}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3239,7 +3653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -3262,7 +3676,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -3285,7 +3699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -3308,7 +3722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -3331,7 +3745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -3354,7 +3768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -3377,7 +3791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -3400,7 +3814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -3423,7 +3837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -3446,7 +3860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -3469,7 +3883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -3492,7 +3906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -3515,7 +3929,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -3538,7 +3952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -3561,7 +3975,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -3584,7 +3998,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -3607,7 +4021,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -3630,7 +4044,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -3653,7 +4067,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -3676,7 +4090,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -3699,7 +4113,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -3722,7 +4136,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -3745,7 +4159,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -3768,7 +4182,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -3791,7 +4205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -3814,7 +4228,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -3837,7 +4251,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -3860,7 +4274,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -3883,7 +4297,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -3906,7 +4320,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3929,7 +4343,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3952,7 +4366,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3975,7 +4389,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3998,7 +4412,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -4021,7 +4435,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -4044,7 +4458,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -4067,7 +4481,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -4090,7 +4504,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -4110,6 +4524,144 @@
         <v>93</v>
       </c>
       <c r="G39" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F40" s="10">
+        <v>93</v>
+      </c>
+      <c r="G40" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F41" s="10">
+        <v>93</v>
+      </c>
+      <c r="G41" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F42" s="10">
+        <v>93</v>
+      </c>
+      <c r="G42" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F43" s="10">
+        <v>93</v>
+      </c>
+      <c r="G43" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F44" s="10">
+        <v>93</v>
+      </c>
+      <c r="G44" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="F45" s="10">
+        <v>93</v>
+      </c>
+      <c r="G45" s="10">
         <v>90</v>
       </c>
     </row>
